--- a/data-manipulation-scripts/sheets-cleanup/sheets/LONA FREIO - 30_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/LONA FREIO - 30_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -40,7 +40,7 @@
     <t>070341173428</t>
   </si>
   <si>
-    <t>LONA FREIO IRON NXR150/ BIZ100/ BIZ 125/ MOBY 50 351240</t>
+    <t>LONA FREIO IRON NXR150/ BIZ100125/ MOBY 50 351240</t>
   </si>
   <si>
     <t>710371771965</t>
@@ -82,13 +82,16 @@
     <t>710371771972</t>
   </si>
   <si>
-    <t>LONA FREIO TRASEIRO 0,5 EXTREMO BIZ125</t>
+    <t>LONA FREIO TRASEIRO 0,50 EXTREMO BIZ125</t>
   </si>
   <si>
     <t>070341173442</t>
   </si>
   <si>
     <t>LONA FREIO IRON YBR125/ XTZ125/ NEO AT115/ MAX125/ CRYPTON115 351238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -397,7 +400,9 @@
       <c r="C2" s="2">
         <v>23.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>23.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -409,7 +414,9 @@
       <c r="C3" s="2">
         <v>6.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>23.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -421,7 +428,9 @@
       <c r="C4" s="2">
         <v>16.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>23.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -433,7 +442,9 @@
       <c r="C5" s="2">
         <v>9.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -445,7 +456,9 @@
       <c r="C6" s="2">
         <v>4.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -457,7 +470,9 @@
       <c r="C7" s="2">
         <v>7.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -469,7 +484,9 @@
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -481,7 +498,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -493,7 +512,9 @@
       <c r="C10" s="2">
         <v>5.0</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -505,7 +526,9 @@
       <c r="C11" s="2">
         <v>16.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -517,20 +540,26 @@
       <c r="C12" s="2">
         <v>12.0</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="2">
+        <v>23.0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4"/>
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
